--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104586_W15.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104586_W15.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.714499999999999</v>
+        <v>9.873799999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3023</v>
+        <v>7.0893</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4122</v>
+        <v>2.7845</v>
       </c>
       <c r="G2" t="n">
-        <v>7.6174</v>
+        <v>7.6003</v>
       </c>
       <c r="H2" t="n">
-        <v>1.4228</v>
+        <v>1.419</v>
       </c>
       <c r="I2" t="n">
-        <v>6.1946</v>
+        <v>6.1813</v>
       </c>
       <c r="J2" t="n">
-        <v>5.8491</v>
+        <v>5.8047</v>
       </c>
       <c r="K2" t="n">
-        <v>0.4809</v>
+        <v>0.4579</v>
       </c>
       <c r="L2" t="n">
-        <v>5.3682</v>
+        <v>5.3468</v>
       </c>
       <c r="M2" t="n">
-        <v>1.7683</v>
+        <v>1.7956</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9419</v>
+        <v>0.9611</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8264</v>
+        <v>0.8345</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.5004</v>
+        <v>-0.3121</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3297</v>
+        <v>0.5201</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.1708</v>
+        <v>-0.8322000000000001</v>
       </c>
       <c r="V2" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="W2" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6826</v>
+        <v>5.5228</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2701</v>
+        <v>4.6458</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4125</v>
+        <v>0.877</v>
       </c>
       <c r="G3" t="n">
-        <v>4.1059</v>
+        <v>4.0932</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5453</v>
+        <v>-0.5511</v>
       </c>
       <c r="I3" t="n">
-        <v>4.6513</v>
+        <v>4.6443</v>
       </c>
       <c r="J3" t="n">
-        <v>4.6298</v>
+        <v>4.5939</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1172</v>
+        <v>0.0959</v>
       </c>
       <c r="L3" t="n">
-        <v>4.5126</v>
+        <v>4.498</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5239</v>
+        <v>-0.5007</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6626</v>
+        <v>-0.6471</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.4499</v>
+        <v>-0.59</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0253</v>
+        <v>-0.602</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4246</v>
+        <v>0.0119</v>
       </c>
       <c r="V3" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="W3" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. BAGAYOKO</t>
+          <t>T. HLINASON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0774</v>
+        <v>1.4523</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8364</v>
+        <v>1.8726</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.759</v>
+        <v>-0.4203</v>
       </c>
       <c r="G4" t="n">
-        <v>2.8503</v>
+        <v>2.6703</v>
       </c>
       <c r="H4" t="n">
-        <v>2.1413</v>
+        <v>1.6855</v>
       </c>
       <c r="I4" t="n">
-        <v>0.709</v>
+        <v>0.9848</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2574</v>
+        <v>1.9368</v>
       </c>
       <c r="K4" t="n">
-        <v>2.0016</v>
+        <v>1.1549</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2558</v>
+        <v>0.782</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5929</v>
+        <v>0.7335</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1397</v>
+        <v>0.5306</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4532</v>
+        <v>0.2028</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1342</v>
+        <v>-1.3658</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9587</v>
+        <v>0.3463</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4597</v>
+        <v>0.5991</v>
       </c>
       <c r="U4" t="n">
-        <v>0.499</v>
+        <v>-0.2527</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.1853</v>
+        <v>-1.792</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2534</v>
+        <v>0.7025</v>
       </c>
       <c r="X4" t="n">
-        <v>-3.4387</v>
+        <v>-2.4945</v>
       </c>
     </row>
     <row r="5">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.713</v>
+        <v>1.4124</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2652</v>
+        <v>-0.5524</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9781</v>
+        <v>1.9647</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5526</v>
+        <v>-0.5446</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0071</v>
+        <v>0.014</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5598</v>
+        <v>-0.5586</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.5132</v>
+        <v>-0.5173</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0866</v>
+        <v>0.0862</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5998</v>
+        <v>-0.6035</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0395</v>
+        <v>-0.0273</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0795</v>
+        <v>-0.0722</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6778</v>
+        <v>0.3635</v>
       </c>
       <c r="T5" t="n">
-        <v>0.248</v>
+        <v>-0.0351</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4298</v>
+        <v>0.3986</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. HLINASON</t>
+          <t>B. BAGAYOKO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6063</v>
+        <v>1.1821</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7466</v>
+        <v>2.2117</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1403</v>
+        <v>-1.0296</v>
       </c>
       <c r="G6" t="n">
-        <v>2.659</v>
+        <v>2.85</v>
       </c>
       <c r="H6" t="n">
-        <v>1.678</v>
+        <v>2.1425</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9809</v>
+        <v>0.7075</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9439</v>
+        <v>2.2308</v>
       </c>
       <c r="K6" t="n">
-        <v>1.1602</v>
+        <v>1.9855</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7837</v>
+        <v>0.2453</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7151</v>
+        <v>0.6192</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5178</v>
+        <v>0.157</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1973</v>
+        <v>0.4622</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2268</v>
+        <v>0.4553</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.361</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5202</v>
+        <v>0.0558</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4567</v>
+        <v>-0.1282</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0635</v>
+        <v>0.184</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.7997</v>
+        <v>-2.1789</v>
       </c>
       <c r="W6" t="n">
-        <v>0.7071</v>
+        <v>1.2472</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.5068</v>
+        <v>-3.4262</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0116</v>
+        <v>0.9061</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0146</v>
+        <v>-0.1831</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0261</v>
+        <v>1.0892</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.6703</v>
+        <v>-0.6773</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.1687</v>
+        <v>-1.1716</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4984</v>
+        <v>0.4944</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.056</v>
+        <v>-0.0911</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.9462</v>
+        <v>-0.9695</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8902</v>
+        <v>0.8783</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6143</v>
+        <v>-0.5861</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2225</v>
+        <v>-0.2022</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3918</v>
+        <v>-0.384</v>
       </c>
       <c r="P7" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8683</v>
+        <v>-0.9582000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5353</v>
+        <v>-0.6532</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.333</v>
+        <v>-0.305</v>
       </c>
       <c r="V7" t="n">
-        <v>1.1892</v>
+        <v>1.1758</v>
       </c>
       <c r="W7" t="n">
-        <v>0.8036</v>
+        <v>0.7887999999999999</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="8">
@@ -1033,19 +1033,19 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1060,10 +1060,10 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1111,19 +1111,19 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1138,10 +1138,10 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9205</v>
+        <v>-0.8343</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0226</v>
+        <v>0.4175</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9431</v>
+        <v>-1.2517</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6664</v>
+        <v>2.6729</v>
       </c>
       <c r="H10" t="n">
-        <v>2.1919</v>
+        <v>2.1914</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4745</v>
+        <v>0.4815</v>
       </c>
       <c r="J10" t="n">
-        <v>3.2648</v>
+        <v>3.2446</v>
       </c>
       <c r="K10" t="n">
-        <v>2.5558</v>
+        <v>2.5371</v>
       </c>
       <c r="L10" t="n">
-        <v>0.709</v>
+        <v>0.7075</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5984</v>
+        <v>-0.5717</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3639</v>
+        <v>-0.3457</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R10" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2543</v>
+        <v>0.3335</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1603</v>
+        <v>0.5874</v>
       </c>
       <c r="U10" t="n">
-        <v>0.094</v>
+        <v>-0.2538</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. NORMANTAS</t>
+          <t>D. HILLIARD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6697</v>
+        <v>-1.8862</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.8165</v>
+        <v>-2.9357</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1468</v>
+        <v>1.0495</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.0419</v>
+        <v>-1.1024</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.9566</v>
+        <v>-1.8471</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0852</v>
+        <v>0.7447</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.0725</v>
+        <v>-1.8795</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.2218</v>
+        <v>-2.1621</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1493</v>
+        <v>0.2826</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0307</v>
+        <v>0.7771</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2652</v>
+        <v>0.3149</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2345</v>
+        <v>0.4622</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6805</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.361</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>2.0415</v>
+        <v>1.1382</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6917</v>
+        <v>-0.1903</v>
       </c>
       <c r="T11" t="n">
-        <v>1.5243</v>
+        <v>0.5177</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8326</v>
+        <v>-0.708</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="W11" t="n">
-        <v>1.0927</v>
+        <v>0.7025</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0927</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="12">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.1077</v>
+        <v>-2.0015</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.1951</v>
+        <v>-1.9063</v>
       </c>
       <c r="F12" t="n">
-        <v>0.08740000000000001</v>
+        <v>-0.09520000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.1574</v>
+        <v>-1.1444</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7645</v>
+        <v>0.7803</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.9219</v>
+        <v>-1.9247</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.4198</v>
+        <v>-1.4333</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6407</v>
+        <v>0.6378</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.0605</v>
+        <v>-2.071</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2625</v>
+        <v>0.2889</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1238</v>
+        <v>0.1426</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="P12" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8992</v>
+        <v>-0.8163</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0948</v>
+        <v>-0.7901</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1957</v>
+        <v>-0.0262</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W12" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. HILLIARD</t>
+          <t>M. NORMANTAS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.6213</v>
+        <v>-2.439</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.3287</v>
+        <v>-2.7142</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7074</v>
+        <v>0.2753</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.108</v>
+        <v>-3.0325</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.8543</v>
+        <v>-2.9554</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7463</v>
+        <v>-0.0771</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.8581</v>
+        <v>-3.0926</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.1513</v>
+        <v>-3.2415</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2931</v>
+        <v>0.1489</v>
       </c>
       <c r="M13" t="n">
-        <v>0.7502</v>
+        <v>0.06</v>
       </c>
       <c r="N13" t="n">
-        <v>0.297</v>
+        <v>0.2861</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4532</v>
+        <v>-0.226</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.1342</v>
+        <v>0.6829</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.2683</v>
+        <v>-1.3658</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1342</v>
+        <v>2.0487</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9255</v>
+        <v>-0.0893</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0907</v>
+        <v>0.6546</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.0162</v>
+        <v>-0.7439</v>
       </c>
       <c r="V13" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0.7071</v>
+        <v>1.0895</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.1607</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="14">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>12.1398</v>
+        <v>12.8437</v>
       </c>
       <c r="E14" t="n">
-        <v>7.5579</v>
+        <v>7.9452</v>
       </c>
       <c r="F14" t="n">
-        <v>4.5817</v>
+        <v>4.8986</v>
       </c>
       <c r="G14" t="n">
-        <v>13.0224</v>
+        <v>13.0407</v>
       </c>
       <c r="H14" t="n">
-        <v>1.3343</v>
+        <v>1.362699999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>11.6881</v>
+        <v>11.6781</v>
       </c>
       <c r="J14" t="n">
-        <v>11.0254</v>
+        <v>10.797</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7236999999999991</v>
+        <v>0.5822000000000007</v>
       </c>
       <c r="L14" t="n">
-        <v>10.3016</v>
+        <v>10.2149</v>
       </c>
       <c r="M14" t="n">
-        <v>1.9972</v>
+        <v>2.2437</v>
       </c>
       <c r="N14" t="n">
-        <v>0.6105</v>
+        <v>0.7803</v>
       </c>
       <c r="O14" t="n">
-        <v>1.3867</v>
+        <v>1.4632</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2682</v>
+        <v>2.276199999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-13.61</v>
+        <v>-13.6579</v>
       </c>
       <c r="R14" t="n">
-        <v>15.8783</v>
+        <v>15.9343</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.5406</v>
+        <v>-1.8571</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0454</v>
+        <v>0.6703</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.4952</v>
+        <v>-2.5273</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.6104999999999998</v>
+        <v>-0.6161999999999994</v>
       </c>
       <c r="W14" t="n">
-        <v>10.1879</v>
+        <v>10.1356</v>
       </c>
       <c r="X14" t="n">
-        <v>-10.7983</v>
+        <v>-10.7519</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. CATE</t>
+          <t>J. RADEBAUGH</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5793</v>
+        <v>1.9694</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0777</v>
+        <v>3.403</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5016</v>
+        <v>-1.4337</v>
       </c>
       <c r="G15" t="n">
-        <v>0.105</v>
+        <v>2.7766</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1689</v>
+        <v>0.7491</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0639</v>
+        <v>2.0274</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2984</v>
+        <v>4.1655</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1865</v>
+        <v>1.2238</v>
       </c>
       <c r="L15" t="n">
-        <v>0.112</v>
+        <v>2.9417</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1935</v>
+        <v>-1.389</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0176</v>
+        <v>-0.4747</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1759</v>
+        <v>-0.9143</v>
       </c>
       <c r="P15" t="n">
-        <v>1.361</v>
+        <v>0.2276</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.4537</v>
+        <v>-0.6829</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8147</v>
+        <v>0.9105</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1133</v>
+        <v>0.2124</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1402</v>
+        <v>-0.2374</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0269</v>
+        <v>0.4498</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0927</v>
+        <v>0.1578</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0927</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Z. HICKS</t>
+          <t>E. CATE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8522999999999999</v>
+        <v>1.6519</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.4504</v>
+        <v>1.4655</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3027</v>
+        <v>0.1864</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7665</v>
+        <v>0.1062</v>
       </c>
       <c r="H16" t="n">
-        <v>0.316</v>
+        <v>0.164</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4505</v>
+        <v>-0.0578</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0546</v>
+        <v>0.2766</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0173</v>
+        <v>0.1649</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0373</v>
+        <v>0.1117</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7118</v>
+        <v>-0.1704</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2986</v>
+        <v>-0.0009</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4132</v>
+        <v>-0.1695</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.3658</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.2268</v>
+        <v>-0.4553</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2268</v>
+        <v>1.8211</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5762</v>
+        <v>0.18</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2782</v>
+        <v>0.5547</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2979</v>
+        <v>-0.3747</v>
       </c>
       <c r="V16" t="n">
-        <v>0.662</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
-        <v>0.662</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. CACOK</t>
+          <t>Z. HICKS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7561</v>
+        <v>1.1746</v>
       </c>
       <c r="E17" t="n">
-        <v>2.4547</v>
+        <v>-0.452</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.6986</v>
+        <v>1.6266</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.4388</v>
+        <v>0.7732</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.509</v>
+        <v>0.3187</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.9298</v>
+        <v>0.4545</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.2699</v>
+        <v>0.0545</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.3819</v>
+        <v>0.0172</v>
       </c>
       <c r="L17" t="n">
-        <v>0.112</v>
+        <v>0.0372</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.1689</v>
+        <v>0.7187</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1272</v>
+        <v>0.3014</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.0417</v>
+        <v>0.4173</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9073</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.8147</v>
+        <v>-0.2276</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9073</v>
+        <v>0.2276</v>
       </c>
       <c r="S17" t="n">
-        <v>3.1188</v>
+        <v>-0.2636</v>
       </c>
       <c r="T17" t="n">
-        <v>2.0325</v>
+        <v>-0.2788</v>
       </c>
       <c r="U17" t="n">
-        <v>1.0864</v>
+        <v>0.0152</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9834000000000001</v>
+        <v>0.665</v>
       </c>
       <c r="W17" t="n">
-        <v>2.5068</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.5234</v>
+        <v>0.665</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. RADEBAUGH</t>
+          <t>D. DEJULIUS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7554999999999999</v>
+        <v>0.3165</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4752</v>
+        <v>-1.044</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.7197</v>
+        <v>1.3605</v>
       </c>
       <c r="G18" t="n">
-        <v>2.7659</v>
+        <v>-2.314</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7401</v>
+        <v>-0.7822</v>
       </c>
       <c r="I18" t="n">
-        <v>2.0258</v>
+        <v>-1.5318</v>
       </c>
       <c r="J18" t="n">
-        <v>4.1775</v>
+        <v>-1.3699</v>
       </c>
       <c r="K18" t="n">
-        <v>1.2295</v>
+        <v>-0.5945</v>
       </c>
       <c r="L18" t="n">
-        <v>2.948</v>
+        <v>-0.7754</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.4116</v>
+        <v>-0.9441000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4894</v>
+        <v>-0.1877</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9222</v>
+        <v>-0.7563</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2268</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.6805</v>
+        <v>-4.0974</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9073</v>
+        <v>2.2763</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9838</v>
+        <v>0.4806</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1825</v>
+        <v>0.4523</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1987</v>
+        <v>0.0283</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2534</v>
+        <v>3.9709</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1607</v>
+        <v>3.9709</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.4141</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. DEJULIUS</t>
+          <t>D. CACOK</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0449</v>
+        <v>-0.8888</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.2466</v>
+        <v>0.9923999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2018</v>
+        <v>-1.8812</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.2704</v>
+        <v>-2.4498</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.7483</v>
+        <v>-0.5302</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.5221</v>
+        <v>-1.9197</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.2989</v>
+        <v>-0.3029</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5417</v>
+        <v>-0.4147</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7572</v>
+        <v>0.1117</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9716</v>
+        <v>-2.1469</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2066</v>
+        <v>-0.1155</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7649</v>
+        <v>-2.0314</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.8147</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.083</v>
+        <v>-1.8211</v>
       </c>
       <c r="R19" t="n">
-        <v>2.2683</v>
+        <v>0.9105</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9448</v>
+        <v>1.4911</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8498</v>
+        <v>0.622</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.095</v>
+        <v>0.8691</v>
       </c>
       <c r="V19" t="n">
-        <v>3.9851</v>
+        <v>0.9805</v>
       </c>
       <c r="W19" t="n">
-        <v>3.9851</v>
+        <v>2.4945</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.5139</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>W. FALK</t>
+          <t>M. FORREST</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1136</v>
+        <v>-1.0139</v>
       </c>
       <c r="E20" t="n">
-        <v>0.35</v>
+        <v>-0.3148</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4635</v>
+        <v>-0.6992</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2026</v>
+        <v>2.7997</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1226</v>
+        <v>1.4502</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0799</v>
+        <v>1.3495</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1514</v>
+        <v>4.0151</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1141</v>
+        <v>1.3789</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0373</v>
+        <v>2.6361</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.354</v>
+        <v>-1.2154</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2368</v>
+        <v>0.0713</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1172</v>
+        <v>-1.2866</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2268</v>
+        <v>-3.4145</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.4537</v>
+        <v>-3.8697</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8868</v>
+        <v>-0.2903</v>
       </c>
       <c r="T20" t="n">
-        <v>0.8771</v>
+        <v>-0.4601</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0097</v>
+        <v>0.1699</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.0246</v>
+        <v>-0.1089</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.2249</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.7997</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. FORREST</t>
+          <t>W. FALK</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2073</v>
+        <v>-1.2056</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5196</v>
+        <v>-0.0136</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6877</v>
+        <v>-1.1919</v>
       </c>
       <c r="G21" t="n">
-        <v>2.7986</v>
+        <v>-0.1992</v>
       </c>
       <c r="H21" t="n">
-        <v>1.4472</v>
+        <v>-0.1235</v>
       </c>
       <c r="I21" t="n">
-        <v>1.3514</v>
+        <v>-0.07580000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>4.0321</v>
+        <v>0.1439</v>
       </c>
       <c r="K21" t="n">
-        <v>1.3853</v>
+        <v>0.1067</v>
       </c>
       <c r="L21" t="n">
-        <v>2.6468</v>
+        <v>0.0372</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.2335</v>
+        <v>-0.3432</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0619</v>
+        <v>-0.2301</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.2954</v>
+        <v>-0.113</v>
       </c>
       <c r="P21" t="n">
-        <v>-3.4025</v>
+        <v>0.2276</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.8562</v>
+        <v>-0.4553</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4537</v>
+        <v>0.6829</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4942</v>
+        <v>0.7872</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6956</v>
+        <v>0.5269</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2014</v>
+        <v>0.2603</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1093</v>
+        <v>-2.0212</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.2292</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1093</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>H. SANT-ROOS</t>
+          <t>T. NAKIC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9734</v>
+        <v>-2.211</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.2863</v>
+        <v>-2.1384</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3129</v>
+        <v>-0.0726</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.0118</v>
+        <v>-2.4188</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9033</v>
+        <v>0.6513</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.1085</v>
+        <v>-3.0701</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.4101</v>
+        <v>-1.0022</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.9493</v>
+        <v>0.4654</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.4608</v>
+        <v>-1.4676</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6017</v>
+        <v>-1.4166</v>
       </c>
       <c r="N22" t="n">
-        <v>0.046</v>
+        <v>0.1859</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-1.6025</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R22" t="n">
-        <v>1.8147</v>
+        <v>1.5934</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6917</v>
+        <v>-0.0199</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6079</v>
+        <v>0.2296</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0838</v>
+        <v>-0.2494</v>
       </c>
       <c r="V22" t="n">
-        <v>0.2763</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.8163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>T. NAKIC</t>
+          <t>H. SANT-ROOS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.0967</v>
+        <v>-2.5548</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.7171</v>
+        <v>-2.9561</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3796</v>
+        <v>0.4013</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.4317</v>
+        <v>-3.0128</v>
       </c>
       <c r="H23" t="n">
-        <v>0.639</v>
+        <v>-0.9019</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.0707</v>
+        <v>-2.1109</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.9932</v>
+        <v>-2.4263</v>
       </c>
       <c r="K23" t="n">
-        <v>0.4676</v>
+        <v>-0.9588</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.4608</v>
+        <v>-1.4676</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.4384</v>
+        <v>-0.5865</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1715</v>
+        <v>0.0568</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.6099</v>
+        <v>-0.6433</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2268</v>
+        <v>0.4553</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5878</v>
+        <v>1.8211</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8919</v>
+        <v>-0.2753</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3629</v>
+        <v>-0.2535</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.529</v>
+        <v>-0.0218</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.278</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.8114</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.6997</v>
+        <v>-3.3229</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.0173</v>
+        <v>-4.0561</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3176</v>
+        <v>0.7332</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.6071</v>
+        <v>-4.6155</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.3707</v>
+        <v>-2.375</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.2364</v>
+        <v>-2.2406</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.6756</v>
+        <v>-3.7164</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.3213</v>
+        <v>-2.3452</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.3542</v>
+        <v>-1.3712</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.9316</v>
+        <v>-0.8992</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.0494</v>
+        <v>-0.0298</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.8822</v>
+        <v>-0.8694</v>
       </c>
       <c r="P24" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R24" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S24" t="n">
-        <v>0.202</v>
+        <v>0.5805</v>
       </c>
       <c r="T24" t="n">
-        <v>0.7924</v>
+        <v>0.7984</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5904</v>
+        <v>-0.2179</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.6556</v>
+        <v>-0.6536999999999999</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.6556</v>
+        <v>-0.6536999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.9473</v>
+        <v>-5.2725</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.8872</v>
+        <v>-1.9636</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.0601</v>
+        <v>-3.3089</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.4962</v>
+        <v>-4.4863</v>
       </c>
       <c r="H25" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0168</v>
       </c>
       <c r="I25" t="n">
-        <v>-4.5047</v>
+        <v>-4.503</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.0637</v>
+        <v>-2.0816</v>
       </c>
       <c r="K25" t="n">
-        <v>0.1834</v>
+        <v>0.1756</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.2471</v>
+        <v>-2.2572</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.4325</v>
+        <v>-2.4047</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.1749</v>
+        <v>-0.1588</v>
       </c>
       <c r="O25" t="n">
-        <v>-2.2576</v>
+        <v>-2.2458</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R25" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S25" t="n">
-        <v>1.8023</v>
+        <v>0.461</v>
       </c>
       <c r="T25" t="n">
-        <v>1.6302</v>
+        <v>0.5732</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1721</v>
+        <v>-0.1122</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-12.1397</v>
+        <v>-11.3571</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.7669</v>
+        <v>-7.0777</v>
       </c>
       <c r="F26" t="n">
-        <v>-5.3726</v>
+        <v>-4.279500000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>-13.0226</v>
+        <v>-13.0407</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.3342</v>
+        <v>-1.3627</v>
       </c>
       <c r="I26" t="n">
-        <v>-11.6883</v>
+        <v>-11.6783</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.9974</v>
+        <v>-2.243699999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.6104999999999998</v>
+        <v>-0.7807000000000006</v>
       </c>
       <c r="L26" t="n">
-        <v>-1.3867</v>
+        <v>-1.4634</v>
       </c>
       <c r="M26" t="n">
-        <v>-11.0255</v>
+        <v>-10.7973</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.7239</v>
+        <v>-0.5821</v>
       </c>
       <c r="O26" t="n">
-        <v>-10.3015</v>
+        <v>-10.2148</v>
       </c>
       <c r="P26" t="n">
-        <v>-2.2684</v>
+        <v>-2.276400000000001</v>
       </c>
       <c r="Q26" t="n">
-        <v>-15.8785</v>
+        <v>-15.9344</v>
       </c>
       <c r="R26" t="n">
-        <v>13.61</v>
+        <v>13.6579</v>
       </c>
       <c r="S26" t="n">
-        <v>2.5406</v>
+        <v>3.3437</v>
       </c>
       <c r="T26" t="n">
-        <v>2.4955</v>
+        <v>2.5273</v>
       </c>
       <c r="U26" t="n">
-        <v>0.04529999999999987</v>
+        <v>0.8165999999999999</v>
       </c>
       <c r="V26" t="n">
-        <v>0.6104999999999998</v>
+        <v>0.6161999999999992</v>
       </c>
       <c r="W26" t="n">
-        <v>8.613099999999999</v>
+        <v>8.572999999999999</v>
       </c>
       <c r="X26" t="n">
-        <v>-8.0025</v>
+        <v>-7.9566</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104586_W15.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104586_W15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104586_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104586_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-2.4945</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104586_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104586_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-3.4262</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104586_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104586_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104586_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104586_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104586_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104586_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104586_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104586_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-10.7519</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104586_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104586_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0.665</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104586_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104586_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.5139</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104586_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104586_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104586_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104586_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.8114</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104586_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-0.6536999999999999</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104586_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104586_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-7.9566</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
